--- a/gex_pivot_levels_2026-10-15.xlsx
+++ b/gex_pivot_levels_2026-10-15.xlsx
@@ -91,6 +91,15 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -98,15 +107,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -544,31 +544,27 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>-$8.41M</t>
+          <t>-$6.85M</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>+$10.42M</t>
+          <t>+$8.49M</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
-        <v>7618.56</v>
+        <v>7628.56</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>7605</v>
+        <v>7615</v>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
@@ -577,31 +573,31 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>-$3.30M</t>
+          <t>-$11.39M</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>+$3.44M</t>
+          <t>+$11.48M</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>7628.56</v>
+        <v>7633.56</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>7615</v>
+        <v>7620</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -610,31 +606,31 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>-$13.84M</t>
+          <t>-$6.38M</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>+$13.94M</t>
+          <t>+$6.57M</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Net</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>7633.56</v>
+        <v>7638.56</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>7620</v>
+        <v>7625</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
@@ -643,31 +639,31 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>-$7.65M</t>
+          <t>-$12.33M</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>+$7.88M</t>
+          <t>+$12.79M</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>7638.56</v>
+        <v>7658.56</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>7625</v>
+        <v>7645</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -676,31 +672,31 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>-$15.02M</t>
+          <t>-$6.17M</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>+$15.58M</t>
+          <t>+$6.50M</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Net</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>7658.56</v>
+        <v>7663.56</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>7645</v>
+        <v>7650</v>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
@@ -709,31 +705,31 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>-$7.01M</t>
+          <t>-$19.15M</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>+$7.39M</t>
+          <t>+$20.66M</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>7663.56</v>
+        <v>7668.56</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>7650</v>
+        <v>7655</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -742,31 +738,31 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>-$21.19M</t>
+          <t>-$5.73M</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>+$22.86M</t>
+          <t>+$6.01M</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Net</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>7668.56</v>
+        <v>7683.56</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>7655</v>
+        <v>7670</v>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
@@ -775,487 +771,487 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>-$6.30M</t>
+          <t>-$25.25M</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>+$6.61M</t>
+          <t>+$26.25M</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Net</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>7683.56</v>
+        <v>7686.36</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>7670</v>
+        <v>765</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>-$20.85M</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>+$28.71M</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>7706.42</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>767</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>+$3.35M</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>+$51.87M</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>7708.56</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>7695</v>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>-$26.09M</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>+$27.12M</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>+$2.21M</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>+$17.52M</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>7713.56</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>7700</v>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>-$1.28M</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>+$38.64M</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>7716.45</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>768</v>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>-$24.93M</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>+$57.21M</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="5" t="n">
-        <v>7686.36</v>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>765</v>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>7723.56</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>7710</v>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>-$5.55M</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>+$13.30M</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>7736.51</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>770</v>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>-$20.85M</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>+$28.71M</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="n">
-        <v>7706.42</v>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>767</v>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>+$3.35M</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>+$51.87M</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="n">
-        <v>7708.56</v>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>7695</v>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>+$13.13M</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>+$114.13M</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>7738.56</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>7725</v>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>+$2.03M</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>+$16.06M</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="n">
-        <v>7713.56</v>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>7700</v>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>-$1.25M</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>+$20.19M</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>7753.56</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>7740</v>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>-$1.14M</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>+$34.40M</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>-$1.31M</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>+$9.43M</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="n">
-        <v>7716.45</v>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>768</v>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>-$24.93M</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>+$57.21M</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="n">
-        <v>7723.56</v>
-      </c>
-      <c r="B16" s="5" t="n">
-        <v>7710</v>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>-$4.78M</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>+$11.46M</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="n">
-        <v>7736.51</v>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>770</v>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>+$13.13M</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>+$114.13M</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="n">
-        <v>7738.56</v>
-      </c>
-      <c r="B18" s="5" t="n">
-        <v>7725</v>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>-$1.02M</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>+$16.57M</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr"/>
+      <c r="G18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>7753.56</v>
+        <v>7756.57</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>7740</v>
+        <v>772</v>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>-$1.06M</t>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>+$79.18M</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>+$7.58M</t>
+          <t>+$145.84M</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr"/>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>7756.57</v>
+        <v>7763.56</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>772</v>
+        <v>7750</v>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>+$3.27M</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>+$23.28M</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>7783.56</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>7770</v>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>+$4.91M</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>+$9.18M</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>7786.66</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>775</v>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>+$79.18M</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>+$145.84M</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="n">
-        <v>7763.56</v>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>7750</v>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>+$31.89M</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>+$62.00M</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>7788.56</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>7775</v>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>+$2.59M</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>+$18.43M</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>+$2.79M</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>+$13.93M</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="n">
-        <v>7786.66</v>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>775</v>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>+$31.89M</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>+$62.00M</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>7813.56</v>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>7800</v>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>+$2.48M</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>+$8.49M</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="n">
-        <v>7788.56</v>
-      </c>
-      <c r="B23" s="5" t="n">
-        <v>7775</v>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>+$2.17M</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>+$10.84M</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="n">
-        <v>7813.56</v>
-      </c>
-      <c r="B24" s="5" t="n">
-        <v>7800</v>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>+$1.77M</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>+$6.06M</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G24"/>
@@ -1320,339 +1316,339 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="5" t="n">
         <v>29480.27</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="5" t="n">
         <v>720</v>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>-$4.73M</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>+$4.93M</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="2" t="n">
         <v>29521.35</v>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="2" t="n">
         <v>721</v>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>-$1.18M</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>+$1.20M</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="2" t="n">
         <v>29647.18</v>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="2" t="n">
         <v>29750</v>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>-$31.15K</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>+$40.73K</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="5" t="n">
         <v>29685.7</v>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="5" t="n">
         <v>725</v>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>-$10.38M</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>+$10.71M</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="5" t="n">
         <v>29697.18</v>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="5" t="n">
         <v>29800</v>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>-$64.69K</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>+$64.69K</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="2" t="n">
         <v>29717.18</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="2" t="n">
         <v>29820</v>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>-$10.78K</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>+$10.78K</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="5" t="n">
         <v>29722.18</v>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="5" t="n">
         <v>29825</v>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>-$88.95K</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>+$88.95K</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="2" t="n">
         <v>29726.79</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="2" t="n">
         <v>726</v>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>-$1.37M</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>+$1.43M</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="2" t="n">
         <v>29737.18</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="2" t="n">
         <v>29840</v>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>-$35.04K</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>+$35.04K</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="5" t="n">
         <v>29747.18</v>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B11" s="5" t="n">
         <v>29850</v>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>-$210.25K</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>+$215.65K</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="2" t="n">
         <v>29767.18</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="2" t="n">
         <v>29870</v>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
@@ -1662,30 +1658,30 @@
           <t>$0</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>+$29.95K</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="2" t="n">
         <v>29787.18</v>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="2" t="n">
         <v>29890</v>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
@@ -1695,63 +1691,63 @@
           <t>$0</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>+$29.95K</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="5" t="n">
         <v>29797.18</v>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B14" s="5" t="n">
         <v>29900</v>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>-$212.65K</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>+$284.53K</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="2" t="n">
         <v>29837.18</v>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="2" t="n">
         <v>29940</v>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
@@ -1761,220 +1757,220 @@
           <t>+$3.00K</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>+$44.93K</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="2" t="n">
         <v>29847.18</v>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="2" t="n">
         <v>29950</v>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>-$41.93K</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>+$143.76K</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr"/>
+      <c r="G16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="5" t="n">
         <v>29891.14</v>
       </c>
-      <c r="B17" s="2" t="n">
+      <c r="B17" s="5" t="n">
         <v>730</v>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>-$12.58M</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>+$13.04M</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="5" t="n">
         <v>29897.18</v>
       </c>
-      <c r="B18" s="2" t="n">
+      <c r="B18" s="5" t="n">
         <v>30000</v>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>-$107.82K</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>+$209.66K</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="2" t="n">
         <v>29932.23</v>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="2" t="n">
         <v>731</v>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>-$1.35M</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>+$1.43M</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="2" t="n">
         <v>29947.18</v>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="B20" s="2" t="n">
         <v>30050</v>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>-$23.96K</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>+$89.85K</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="5" t="n">
         <v>29973.32</v>
       </c>
-      <c r="B21" s="2" t="n">
+      <c r="B21" s="5" t="n">
         <v>732</v>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>-$3.77M</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>+$3.87M</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="5" t="n">
         <v>29997.18</v>
       </c>
-      <c r="B22" s="2" t="n">
+      <c r="B22" s="5" t="n">
         <v>30100</v>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
@@ -1984,154 +1980,154 @@
           <t>+$119.80K</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>+$167.72K</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="2" t="n">
         <v>30014.4</v>
       </c>
-      <c r="B23" s="5" t="n">
+      <c r="B23" s="2" t="n">
         <v>733</v>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>-$1.13M</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>+$1.25M</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="5" t="n">
         <v>30096.58</v>
       </c>
-      <c r="B24" s="2" t="n">
+      <c r="B24" s="5" t="n">
         <v>735</v>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>-$8.96M</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>+$10.39M</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="2" t="n">
         <v>30219.84</v>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="B25" s="2" t="n">
         <v>738</v>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>-$4.09M</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>+$4.51M</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="2" t="n">
         <v>30302.02</v>
       </c>
-      <c r="B26" s="5" t="n">
+      <c r="B26" s="2" t="n">
         <v>740</v>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>-$2.02M</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>+$3.59M</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr"/>
+      <c r="G26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="2" t="n">
         <v>30425.28</v>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B27" s="2" t="n">
         <v>743</v>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
@@ -2141,26 +2137,26 @@
           <t>+$1.35M</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>+$4.49M</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr"/>
+      <c r="G27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="2" t="n">
         <v>30712.89</v>
       </c>
-      <c r="B28" s="5" t="n">
+      <c r="B28" s="2" t="n">
         <v>750</v>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
@@ -2170,17 +2166,17 @@
           <t>+$1.43M</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>+$1.71M</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr"/>
+      <c r="G28" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G28"/>
@@ -2245,128 +2241,128 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="2" t="n">
         <v>2515</v>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B2" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>IWM</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>-$923.35K</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>+$923.53K</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="5" t="n">
         <v>2706.14</v>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="5" t="n">
         <v>269</v>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>IWM</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>-$4.98M</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>+$5.50M</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="2" t="n">
         <v>2716.2</v>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="2" t="n">
         <v>270</v>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>IWM</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>-$2.34M</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>+$2.46M</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="5" t="n">
         <v>2726.26</v>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="5" t="n">
         <v>271</v>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>IWM</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>-$9.80M</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>+$10.82M</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
@@ -2435,104 +2431,104 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="2" t="n">
         <v>85.70999999999999</v>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B2" s="2" t="n">
         <v>140</v>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>-$764.61K</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>+$1.62M</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="2" t="n">
         <v>88.77</v>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="2" t="n">
         <v>145</v>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>-$1.23M</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>+$4.08M</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="5" t="n">
         <v>90.61</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="5" t="n">
         <v>148</v>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>-$2.10M</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>+$3.36M</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="5" t="n">
         <v>91.83</v>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
@@ -2542,30 +2538,30 @@
           <t>+$5.49M</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>+$13.77M</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="2" t="n">
         <v>93.67</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="2" t="n">
         <v>153</v>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
@@ -2575,26 +2571,26 @@
           <t>+$513.61K</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>+$2.96M</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="2" t="n">
         <v>94.28</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="2" t="n">
         <v>154</v>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
@@ -2604,30 +2600,30 @@
           <t>+$287.63K</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>+$1.46M</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="5" t="n">
         <v>94.89</v>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="5" t="n">
         <v>155</v>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
@@ -2637,30 +2633,30 @@
           <t>+$8.12M</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>+$10.89M</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="2" t="n">
         <v>96.42</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="2" t="n">
         <v>157.5</v>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
@@ -2670,30 +2666,30 @@
           <t>+$201.28K</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>+$225.63K</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="5" t="n">
         <v>97.95</v>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" s="5" t="n">
         <v>160</v>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
@@ -2703,17 +2699,17 @@
           <t>+$3.14M</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>+$3.83M</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -2782,236 +2778,236 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="5" t="n">
         <v>3995.78</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>-$5.23M</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>+$5.95M</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="2" t="n">
         <v>4045.73</v>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="2" t="n">
         <v>81</v>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>-$2.76M</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>+$3.04M</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="5" t="n">
         <v>4145.62</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="5" t="n">
         <v>83</v>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>-$6.24M</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>+$6.95M</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="2" t="n">
         <v>4154.63</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="2" t="n">
         <v>375</v>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>-$642.07K</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>+$4.65M</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="2" t="n">
         <v>4165.71</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="2" t="n">
         <v>376</v>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>-$1.57M</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>+$2.02M</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="2" t="n">
         <v>4170.59</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="2" t="n">
         <v>83.5</v>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>-$400.53K</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>+$424.51K</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="2" t="n">
         <v>4210.03</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="2" t="n">
         <v>380</v>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>-$63.56K</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>+$1.13M</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="5" t="n">
         <v>4232.18</v>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B9" s="5" t="n">
         <v>382</v>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
@@ -3021,92 +3017,92 @@
           <t>+$684.50K</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>+$818.03K</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="5" t="n">
         <v>4245.52</v>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" s="5" t="n">
         <v>85</v>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>-$8.84M</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>+$12.43M</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="2" t="n">
         <v>4345.41</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="2" t="n">
         <v>87</v>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>-$1.17M</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>+$2.16M</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="5" t="n">
         <v>4420.33</v>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B12" s="5" t="n">
         <v>88.5</v>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
@@ -3116,30 +3112,30 @@
           <t>+$3.36M</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>+$3.79M</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="2" t="n">
         <v>4470.28</v>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="2" t="n">
         <v>89.5</v>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
@@ -3149,30 +3145,30 @@
           <t>+$4.82K</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>+$98.09K</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="2" t="n">
         <v>4495.25</v>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
@@ -3182,26 +3178,26 @@
           <t>+$203.63K</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>+$3.38M</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr"/>
+      <c r="G14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="2" t="n">
         <v>4520.23</v>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="2" t="n">
         <v>90.5</v>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
@@ -3211,30 +3207,30 @@
           <t>+$2.75M</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>+$2.75M</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="2" t="n">
         <v>4670.07</v>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="2" t="n">
         <v>93.5</v>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
@@ -3244,17 +3240,17 @@
           <t>+$978.82K</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>+$985.06K</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr"/>
+      <c r="G16" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G16"/>
@@ -3325,18 +3321,18 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="5" t="n">
         <v>7756.57</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="5" t="n">
         <v>772</v>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
@@ -3346,35 +3342,35 @@
           <t>+$79.18M</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>+$145.84M</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="2" t="n">
         <v>7736.51</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="2" t="n">
         <v>770</v>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
@@ -3384,31 +3380,31 @@
           <t>+$13.13M</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>+$114.13M</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="2" t="n">
         <v>7786.66</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="2" t="n">
         <v>775</v>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
@@ -3418,69 +3414,69 @@
           <t>+$31.89M</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>+$62.00M</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="2" t="n">
         <v>7716.45</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="2" t="n">
         <v>768</v>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>-$24.93M</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>+$57.21M</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="2" t="n">
         <v>7706.42</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="2" t="n">
         <v>767</v>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
@@ -3490,127 +3486,127 @@
           <t>+$3.35M</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>+$51.87M</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="2" t="n">
         <v>7713.56</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="2" t="n">
         <v>7700</v>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>-$1.14M</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>+$34.40M</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>-$1.28M</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>+$38.64M</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="2" t="n">
         <v>7686.36</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="2" t="n">
         <v>765</v>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>-$20.85M</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>+$28.71M</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B9" s="5" t="n">
         <v>7683.56</v>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="C9" s="5" t="n">
         <v>7670</v>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>-$26.09M</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>+$27.12M</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>-$25.25M</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>+$26.25M</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
@@ -3623,36 +3619,32 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>7663.56</v>
+        <v>7763.56</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>7650</v>
+        <v>7750</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>-$21.19M</t>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>+$3.27M</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>+$22.86M</t>
+          <t>+$23.28M</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -3661,100 +3653,104 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>7763.56</v>
+        <v>7663.56</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>7750</v>
+        <v>7650</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>+$2.59M</t>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>-$19.15M</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>+$18.43M</t>
+          <t>+$20.66M</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>7738.56</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>7725</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>-$1.25M</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>+$20.19M</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n">
-        <v>7738.56</v>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>7725</v>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="B13" s="2" t="n">
+        <v>7708.56</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>7695</v>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>-$1.02M</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>+$16.57M</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>7708.56</v>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>7695</v>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>+$2.03M</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>+$16.06M</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
+          <t>+$2.21M</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>+$17.52M</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -3767,184 +3763,180 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>7638.56</v>
+        <v>7788.56</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>7625</v>
+        <v>7775</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>-$15.02M</t>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>+$2.79M</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>+$15.58M</t>
+          <t>+$13.93M</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>91.83</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>+$5.49M</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>+$13.77M</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>7628.56</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>7615</v>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>-$13.84M</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>+$13.94M</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>91.83</v>
+        <v>7723.56</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>150</v>
+        <v>7710</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>+$5.49M</t>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>-$5.55M</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>+$13.77M</t>
+          <t>+$13.30M</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>29891.14</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>730</v>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>-$12.58M</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>+$13.04M</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>29891.14</v>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>730</v>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>-$12.58M</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>+$13.04M</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>7638.56</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>7625</v>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>-$12.33M</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>+$12.79M</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>4245.52</v>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>85</v>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>-$8.84M</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>+$12.43M</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
@@ -3953,222 +3945,226 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>4245.52</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>-$8.84M</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>+$12.43M</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n">
-        <v>7723.56</v>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>7710</v>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="B20" s="5" t="n">
+        <v>7628.56</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>7615</v>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>-$4.78M</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>+$11.46M</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>-$11.39M</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>+$11.48M</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>94.89</v>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>155</v>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>+$8.12M</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>+$10.89M</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>7788.56</v>
+        <v>94.89</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>7775</v>
+        <v>155</v>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>+$2.17M</t>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>+$8.12M</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>+$10.84M</t>
+          <t>+$10.89M</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="inlineStr"/>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>RTY</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n">
+      <c r="B22" s="5" t="n">
         <v>2726.26</v>
       </c>
-      <c r="C22" s="2" t="n">
+      <c r="C22" s="5" t="n">
         <v>271</v>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>IWM</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>-$9.80M</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>+$10.82M</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B23" s="2" t="n">
+      <c r="B23" s="5" t="n">
         <v>29685.7</v>
       </c>
-      <c r="C23" s="2" t="n">
+      <c r="C23" s="5" t="n">
         <v>725</v>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>-$10.38M</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t>+$10.71M</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>7613.56</v>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>7600</v>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>-$8.41M</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>+$10.42M</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>30096.58</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>735</v>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>-$8.96M</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>+$10.39M</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
@@ -4177,370 +4173,366 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>30096.58</v>
+        <v>7753.56</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>735</v>
+        <v>7740</v>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>SPX</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>-$8.96M</t>
+          <t>-$1.31M</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>+$10.39M</t>
+          <t>+$9.43M</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>7783.56</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>7770</v>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>+$4.91M</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>+$9.18M</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>7613.56</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>7600</v>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>-$6.85M</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>+$8.49M</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>7813.56</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>7800</v>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>+$2.48M</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>+$8.49M</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>4145.62</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>83</v>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>-$6.24M</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>+$6.95M</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="H29" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n">
+      <c r="B30" s="2" t="n">
         <v>7633.56</v>
       </c>
-      <c r="C26" s="5" t="n">
+      <c r="C30" s="2" t="n">
         <v>7620</v>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>-$7.65M</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>+$7.88M</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>-$6.38M</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>+$6.57M</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H26" s="6" t="inlineStr">
+      <c r="H30" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n">
-        <v>7753.56</v>
-      </c>
-      <c r="C27" s="5" t="n">
-        <v>7740</v>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="B31" s="2" t="n">
+        <v>7658.56</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>7645</v>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>-$1.06M</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>+$7.58M</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="n">
-        <v>7658.56</v>
-      </c>
-      <c r="C28" s="5" t="n">
-        <v>7645</v>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>-$7.01M</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>+$7.39M</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>-$6.17M</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>+$6.50M</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H28" s="6" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>4145.62</v>
-      </c>
-      <c r="C29" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>-$6.24M</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>+$6.95M</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="n">
-        <v>7668.56</v>
-      </c>
-      <c r="C30" s="5" t="n">
-        <v>7655</v>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>-$6.30M</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>+$6.61M</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="n">
-        <v>7813.56</v>
-      </c>
-      <c r="C31" s="5" t="n">
-        <v>7800</v>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t>+$1.77M</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>+$6.06M</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>7668.56</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>7655</v>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>-$5.73M</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>+$6.01M</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="B32" s="2" t="n">
+      <c r="B33" s="5" t="n">
         <v>3995.78</v>
       </c>
-      <c r="C32" s="2" t="n">
+      <c r="C33" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>-$5.23M</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <t>+$5.95M</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="G33" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="H33" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>RTY</t>
         </is>
       </c>
-      <c r="B33" s="2" t="n">
+      <c r="B34" s="5" t="n">
         <v>2706.14</v>
       </c>
-      <c r="C33" s="2" t="n">
+      <c r="C34" s="5" t="n">
         <v>269</v>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>IWM</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E34" s="7" t="inlineStr">
         <is>
           <t>-$4.98M</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <t>+$5.50M</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G34" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>29480.27</v>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>720</v>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>-$4.73M</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>+$4.93M</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="H34" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
@@ -4549,248 +4541,248 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>29480.27</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>720</v>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>-$4.73M</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>+$4.93M</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="B35" s="5" t="n">
+      <c r="B36" s="2" t="n">
         <v>4154.63</v>
       </c>
-      <c r="C35" s="5" t="n">
+      <c r="C36" s="2" t="n">
         <v>375</v>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>-$642.07K</t>
         </is>
       </c>
-      <c r="F35" s="6" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t>+$4.65M</t>
         </is>
       </c>
-      <c r="G35" s="6" t="inlineStr">
+      <c r="G36" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H35" s="6" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="H36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B36" s="5" t="n">
+      <c r="B37" s="2" t="n">
         <v>30219.84</v>
       </c>
-      <c r="C36" s="5" t="n">
+      <c r="C37" s="2" t="n">
         <v>738</v>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>-$4.09M</t>
         </is>
       </c>
-      <c r="F36" s="6" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>+$4.51M</t>
         </is>
       </c>
-      <c r="G36" s="6" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H36" s="6" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B37" s="5" t="n">
+      <c r="B38" s="2" t="n">
         <v>30425.28</v>
       </c>
-      <c r="C37" s="5" t="n">
+      <c r="C38" s="2" t="n">
         <v>743</v>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E37" s="8" t="inlineStr">
+      <c r="E38" s="8" t="inlineStr">
         <is>
           <t>+$1.35M</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr">
+      <c r="F38" s="3" t="inlineStr">
         <is>
           <t>+$4.49M</t>
         </is>
       </c>
-      <c r="G37" s="6" t="inlineStr">
+      <c r="G38" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H37" s="6" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="n">
-        <v>88.77</v>
-      </c>
-      <c r="C38" s="5" t="n">
-        <v>145</v>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>-$1.23M</t>
-        </is>
-      </c>
-      <c r="F38" s="6" t="inlineStr">
-        <is>
-          <t>+$4.08M</t>
-        </is>
-      </c>
-      <c r="G38" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H38" s="6" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>88.77</v>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>-$1.23M</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>+$4.08M</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B39" s="2" t="n">
+      <c r="B40" s="5" t="n">
         <v>29973.32</v>
       </c>
-      <c r="C39" s="2" t="n">
+      <c r="C40" s="5" t="n">
         <v>732</v>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="E40" s="7" t="inlineStr">
         <is>
           <t>-$3.77M</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="F40" s="6" t="inlineStr">
         <is>
           <t>+$3.87M</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="G40" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="H40" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="B40" s="2" t="n">
+      <c r="B41" s="5" t="n">
         <v>97.95</v>
       </c>
-      <c r="C40" s="2" t="n">
+      <c r="C41" s="5" t="n">
         <v>160</v>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="E40" s="9" t="inlineStr">
+      <c r="E41" s="9" t="inlineStr">
         <is>
           <t>+$3.14M</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr">
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <t>+$3.83M</t>
         </is>
       </c>
-      <c r="G40" s="3" t="inlineStr">
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n">
-        <v>4420.33</v>
-      </c>
-      <c r="C41" s="2" t="n">
-        <v>88.5</v>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E41" s="9" t="inlineStr">
-        <is>
-          <t>+$3.36M</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>+$3.79M</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
+      <c r="H41" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -4799,1394 +4791,1394 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>4420.33</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>+$3.36M</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>+$3.79M</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B42" s="5" t="n">
+      <c r="B43" s="2" t="n">
         <v>30302.02</v>
       </c>
-      <c r="C42" s="5" t="n">
+      <c r="C43" s="2" t="n">
         <v>740</v>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E43" s="4" t="inlineStr">
         <is>
           <t>-$2.02M</t>
         </is>
       </c>
-      <c r="F42" s="6" t="inlineStr">
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>+$3.59M</t>
         </is>
       </c>
-      <c r="G42" s="6" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H42" s="6" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="n">
-        <v>7618.56</v>
-      </c>
-      <c r="C43" s="5" t="n">
-        <v>7605</v>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>-$3.30M</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="inlineStr">
-        <is>
-          <t>+$3.44M</t>
-        </is>
-      </c>
-      <c r="G43" s="6" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>4495.25</v>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>+$203.63K</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>+$3.38M</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>90.61</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>148</v>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>-$2.10M</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>+$3.36M</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>4045.73</v>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>-$2.76M</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>+$3.04M</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H43" s="6" t="inlineStr">
+      <c r="H46" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>93.67</v>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>153</v>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>+$513.61K</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>+$2.96M</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="B44" s="5" t="n">
-        <v>4495.25</v>
-      </c>
-      <c r="C44" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
+      <c r="B48" s="2" t="n">
+        <v>4520.23</v>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
       </c>
-      <c r="E44" s="8" t="inlineStr">
-        <is>
-          <t>+$203.63K</t>
-        </is>
-      </c>
-      <c r="F44" s="6" t="inlineStr">
-        <is>
-          <t>+$3.38M</t>
-        </is>
-      </c>
-      <c r="G44" s="6" t="inlineStr">
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>+$2.75M</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>+$2.75M</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>RTY</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>2716.2</v>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>270</v>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>-$2.34M</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>+$2.46M</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>4345.41</v>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>-$1.17M</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>+$2.16M</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H44" s="6" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="H50" s="3" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>4165.71</v>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>376</v>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>-$1.57M</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>+$2.02M</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>30712.89</v>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>750</v>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>+$1.43M</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>+$1.71M</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="B45" s="2" t="n">
-        <v>90.61</v>
-      </c>
-      <c r="C45" s="2" t="n">
-        <v>148</v>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="B53" s="2" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>-$2.10M</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>+$3.36M</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>-$764.61K</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>+$1.62M</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>94.28</v>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>154</v>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>+$287.63K</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>+$1.46M</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>29726.79</v>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>726</v>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>-$1.37M</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>+$1.43M</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>29932.23</v>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>731</v>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>-$1.35M</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>+$1.43M</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>30014.4</v>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>733</v>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>-$1.13M</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>+$1.25M</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>29521.35</v>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>721</v>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>-$1.18M</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>+$1.20M</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>4210.03</v>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>380</v>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>-$63.56K</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>+$1.13M</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>4670.07</v>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>+$978.82K</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>+$985.06K</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>RTY</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>2515</v>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>-$923.35K</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>+$923.53K</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>4232.18</v>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>382</v>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E62" s="9" t="inlineStr">
+        <is>
+          <t>+$684.50K</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>+$818.03K</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr">
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>4170.59</v>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>-$400.53K</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>+$424.51K</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>29797.18</v>
+      </c>
+      <c r="C64" s="5" t="n">
+        <v>29900</v>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>-$212.65K</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>+$284.53K</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>96.42</v>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>157.5</v>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>+$201.28K</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>+$225.63K</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>29747.18</v>
+      </c>
+      <c r="C66" s="5" t="n">
+        <v>29850</v>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>-$210.25K</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>+$215.65K</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>29897.18</v>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>-$107.82K</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>+$209.66K</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>29997.18</v>
+      </c>
+      <c r="C68" s="5" t="n">
+        <v>30100</v>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>+$119.80K</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>+$167.72K</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>29847.18</v>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>29950</v>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>-$41.93K</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>+$143.76K</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="B46" s="5" t="n">
-        <v>4045.73</v>
-      </c>
-      <c r="C46" s="5" t="n">
-        <v>81</v>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="B70" s="2" t="n">
+        <v>4470.28</v>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
       </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>-$2.76M</t>
-        </is>
-      </c>
-      <c r="F46" s="6" t="inlineStr">
-        <is>
-          <t>+$3.04M</t>
-        </is>
-      </c>
-      <c r="G46" s="6" t="inlineStr">
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>+$4.82K</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>+$98.09K</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H46" s="6" t="inlineStr">
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>29947.18</v>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>30050</v>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>-$23.96K</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>+$89.85K</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>29722.18</v>
+      </c>
+      <c r="C72" s="5" t="n">
+        <v>29825</v>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>-$88.95K</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>+$88.95K</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>29697.18</v>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>29800</v>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>-$64.69K</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>+$64.69K</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>29837.18</v>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>29940</v>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>+$3.00K</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>+$44.93K</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="n">
-        <v>93.67</v>
-      </c>
-      <c r="C47" s="5" t="n">
-        <v>153</v>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E47" s="8" t="inlineStr">
-        <is>
-          <t>+$513.61K</t>
-        </is>
-      </c>
-      <c r="F47" s="6" t="inlineStr">
-        <is>
-          <t>+$2.96M</t>
-        </is>
-      </c>
-      <c r="G47" s="6" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>29647.18</v>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>29750</v>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>-$31.15K</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>+$40.73K</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H47" s="6" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="n">
-        <v>4520.23</v>
-      </c>
-      <c r="C48" s="5" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E48" s="8" t="inlineStr">
-        <is>
-          <t>+$2.75M</t>
-        </is>
-      </c>
-      <c r="F48" s="6" t="inlineStr">
-        <is>
-          <t>+$2.75M</t>
-        </is>
-      </c>
-      <c r="G48" s="6" t="inlineStr">
+      <c r="H75" s="3" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>29737.18</v>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>29840</v>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>-$35.04K</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>+$35.04K</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H48" s="6" t="inlineStr">
+      <c r="H76" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>RTY</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="n">
-        <v>2716.2</v>
-      </c>
-      <c r="C49" s="5" t="n">
-        <v>270</v>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>IWM</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>-$2.34M</t>
-        </is>
-      </c>
-      <c r="F49" s="6" t="inlineStr">
-        <is>
-          <t>+$2.46M</t>
-        </is>
-      </c>
-      <c r="G49" s="6" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>29767.18</v>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>29870</v>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>+$29.95K</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H49" s="6" t="inlineStr">
+      <c r="H77" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="n">
-        <v>4345.41</v>
-      </c>
-      <c r="C50" s="5" t="n">
-        <v>87</v>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E50" s="7" t="inlineStr">
-        <is>
-          <t>-$1.17M</t>
-        </is>
-      </c>
-      <c r="F50" s="6" t="inlineStr">
-        <is>
-          <t>+$2.16M</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H50" s="6" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="n">
-        <v>4165.71</v>
-      </c>
-      <c r="C51" s="5" t="n">
-        <v>376</v>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>-$1.57M</t>
-        </is>
-      </c>
-      <c r="F51" s="6" t="inlineStr">
-        <is>
-          <t>+$2.02M</t>
-        </is>
-      </c>
-      <c r="G51" s="6" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="n">
+        <v>29787.18</v>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>29890</v>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>+$29.95K</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H51" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B52" s="5" t="n">
-        <v>30712.89</v>
-      </c>
-      <c r="C52" s="5" t="n">
-        <v>750</v>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E52" s="8" t="inlineStr">
-        <is>
-          <t>+$1.43M</t>
-        </is>
-      </c>
-      <c r="F52" s="6" t="inlineStr">
-        <is>
-          <t>+$1.71M</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H52" s="6" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="n">
-        <v>85.70999999999999</v>
-      </c>
-      <c r="C53" s="5" t="n">
-        <v>140</v>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>-$764.61K</t>
-        </is>
-      </c>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>+$1.62M</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H53" s="6" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="n">
-        <v>94.28</v>
-      </c>
-      <c r="C54" s="5" t="n">
-        <v>154</v>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E54" s="8" t="inlineStr">
-        <is>
-          <t>+$287.63K</t>
-        </is>
-      </c>
-      <c r="F54" s="6" t="inlineStr">
-        <is>
-          <t>+$1.46M</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="inlineStr">
+      <c r="B79" s="2" t="n">
+        <v>29717.18</v>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>29820</v>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>-$10.78K</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>+$10.78K</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H54" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="n">
-        <v>29726.79</v>
-      </c>
-      <c r="C55" s="5" t="n">
-        <v>726</v>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>-$1.37M</t>
-        </is>
-      </c>
-      <c r="F55" s="6" t="inlineStr">
-        <is>
-          <t>+$1.43M</t>
-        </is>
-      </c>
-      <c r="G55" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H55" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="n">
-        <v>29932.23</v>
-      </c>
-      <c r="C56" s="5" t="n">
-        <v>731</v>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t>-$1.35M</t>
-        </is>
-      </c>
-      <c r="F56" s="6" t="inlineStr">
-        <is>
-          <t>+$1.43M</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H56" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="n">
-        <v>30014.4</v>
-      </c>
-      <c r="C57" s="5" t="n">
-        <v>733</v>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
-          <t>-$1.13M</t>
-        </is>
-      </c>
-      <c r="F57" s="6" t="inlineStr">
-        <is>
-          <t>+$1.25M</t>
-        </is>
-      </c>
-      <c r="G57" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H57" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="n">
-        <v>29521.35</v>
-      </c>
-      <c r="C58" s="5" t="n">
-        <v>721</v>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E58" s="7" t="inlineStr">
-        <is>
-          <t>-$1.18M</t>
-        </is>
-      </c>
-      <c r="F58" s="6" t="inlineStr">
-        <is>
-          <t>+$1.20M</t>
-        </is>
-      </c>
-      <c r="G58" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H58" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="n">
-        <v>4210.03</v>
-      </c>
-      <c r="C59" s="5" t="n">
-        <v>380</v>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E59" s="7" t="inlineStr">
-        <is>
-          <t>-$63.56K</t>
-        </is>
-      </c>
-      <c r="F59" s="6" t="inlineStr">
-        <is>
-          <t>+$1.13M</t>
-        </is>
-      </c>
-      <c r="G59" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H59" s="6" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="n">
-        <v>4670.07</v>
-      </c>
-      <c r="C60" s="5" t="n">
-        <v>93.5</v>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E60" s="8" t="inlineStr">
-        <is>
-          <t>+$978.82K</t>
-        </is>
-      </c>
-      <c r="F60" s="6" t="inlineStr">
-        <is>
-          <t>+$985.06K</t>
-        </is>
-      </c>
-      <c r="G60" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H60" s="6" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>RTY</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="n">
-        <v>2515</v>
-      </c>
-      <c r="C61" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>IWM</t>
-        </is>
-      </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>-$923.35K</t>
-        </is>
-      </c>
-      <c r="F61" s="6" t="inlineStr">
-        <is>
-          <t>+$923.53K</t>
-        </is>
-      </c>
-      <c r="G61" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H61" s="6" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="n">
-        <v>4232.18</v>
-      </c>
-      <c r="C62" s="2" t="n">
-        <v>382</v>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E62" s="9" t="inlineStr">
-        <is>
-          <t>+$684.50K</t>
-        </is>
-      </c>
-      <c r="F62" s="3" t="inlineStr">
-        <is>
-          <t>+$818.03K</t>
-        </is>
-      </c>
-      <c r="G62" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B63" s="5" t="n">
-        <v>4170.59</v>
-      </c>
-      <c r="C63" s="5" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E63" s="7" t="inlineStr">
-        <is>
-          <t>-$400.53K</t>
-        </is>
-      </c>
-      <c r="F63" s="6" t="inlineStr">
-        <is>
-          <t>+$424.51K</t>
-        </is>
-      </c>
-      <c r="G63" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H63" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="n">
-        <v>29797.18</v>
-      </c>
-      <c r="C64" s="2" t="n">
-        <v>29900</v>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>-$212.65K</t>
-        </is>
-      </c>
-      <c r="F64" s="3" t="inlineStr">
-        <is>
-          <t>+$284.53K</t>
-        </is>
-      </c>
-      <c r="G64" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B65" s="5" t="n">
-        <v>96.42</v>
-      </c>
-      <c r="C65" s="5" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E65" s="8" t="inlineStr">
-        <is>
-          <t>+$201.28K</t>
-        </is>
-      </c>
-      <c r="F65" s="6" t="inlineStr">
-        <is>
-          <t>+$225.63K</t>
-        </is>
-      </c>
-      <c r="G65" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H65" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="n">
-        <v>29747.18</v>
-      </c>
-      <c r="C66" s="2" t="n">
-        <v>29850</v>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>-$210.25K</t>
-        </is>
-      </c>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t>+$215.65K</t>
-        </is>
-      </c>
-      <c r="G66" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="n">
-        <v>29897.18</v>
-      </c>
-      <c r="C67" s="2" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>-$107.82K</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="inlineStr">
-        <is>
-          <t>+$209.66K</t>
-        </is>
-      </c>
-      <c r="G67" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="n">
-        <v>29997.18</v>
-      </c>
-      <c r="C68" s="2" t="n">
-        <v>30100</v>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E68" s="9" t="inlineStr">
-        <is>
-          <t>+$119.80K</t>
-        </is>
-      </c>
-      <c r="F68" s="3" t="inlineStr">
-        <is>
-          <t>+$167.72K</t>
-        </is>
-      </c>
-      <c r="G68" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B69" s="5" t="n">
-        <v>29847.18</v>
-      </c>
-      <c r="C69" s="5" t="n">
-        <v>29950</v>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E69" s="7" t="inlineStr">
-        <is>
-          <t>-$41.93K</t>
-        </is>
-      </c>
-      <c r="F69" s="6" t="inlineStr">
-        <is>
-          <t>+$143.76K</t>
-        </is>
-      </c>
-      <c r="G69" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H69" s="6" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B70" s="5" t="n">
-        <v>4470.28</v>
-      </c>
-      <c r="C70" s="5" t="n">
-        <v>89.5</v>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E70" s="8" t="inlineStr">
-        <is>
-          <t>+$4.82K</t>
-        </is>
-      </c>
-      <c r="F70" s="6" t="inlineStr">
-        <is>
-          <t>+$98.09K</t>
-        </is>
-      </c>
-      <c r="G70" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H70" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B71" s="5" t="n">
-        <v>29947.18</v>
-      </c>
-      <c r="C71" s="5" t="n">
-        <v>30050</v>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E71" s="7" t="inlineStr">
-        <is>
-          <t>-$23.96K</t>
-        </is>
-      </c>
-      <c r="F71" s="6" t="inlineStr">
-        <is>
-          <t>+$89.85K</t>
-        </is>
-      </c>
-      <c r="G71" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H71" s="6" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="n">
-        <v>29722.18</v>
-      </c>
-      <c r="C72" s="2" t="n">
-        <v>29825</v>
-      </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>-$88.95K</t>
-        </is>
-      </c>
-      <c r="F72" s="3" t="inlineStr">
-        <is>
-          <t>+$88.95K</t>
-        </is>
-      </c>
-      <c r="G72" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="n">
-        <v>29697.18</v>
-      </c>
-      <c r="C73" s="2" t="n">
-        <v>29800</v>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>-$64.69K</t>
-        </is>
-      </c>
-      <c r="F73" s="3" t="inlineStr">
-        <is>
-          <t>+$64.69K</t>
-        </is>
-      </c>
-      <c r="G73" s="3" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B74" s="5" t="n">
-        <v>29837.18</v>
-      </c>
-      <c r="C74" s="5" t="n">
-        <v>29940</v>
-      </c>
-      <c r="D74" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E74" s="8" t="inlineStr">
-        <is>
-          <t>+$3.00K</t>
-        </is>
-      </c>
-      <c r="F74" s="6" t="inlineStr">
-        <is>
-          <t>+$44.93K</t>
-        </is>
-      </c>
-      <c r="G74" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H74" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B75" s="5" t="n">
-        <v>29647.18</v>
-      </c>
-      <c r="C75" s="5" t="n">
-        <v>29750</v>
-      </c>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E75" s="7" t="inlineStr">
-        <is>
-          <t>-$31.15K</t>
-        </is>
-      </c>
-      <c r="F75" s="6" t="inlineStr">
-        <is>
-          <t>+$40.73K</t>
-        </is>
-      </c>
-      <c r="G75" s="6" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H75" s="6" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B76" s="5" t="n">
-        <v>29737.18</v>
-      </c>
-      <c r="C76" s="5" t="n">
-        <v>29840</v>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t>-$35.04K</t>
-        </is>
-      </c>
-      <c r="F76" s="6" t="inlineStr">
-        <is>
-          <t>+$35.04K</t>
-        </is>
-      </c>
-      <c r="G76" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H76" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B77" s="5" t="n">
-        <v>29767.18</v>
-      </c>
-      <c r="C77" s="5" t="n">
-        <v>29870</v>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E77" s="8" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="F77" s="6" t="inlineStr">
-        <is>
-          <t>+$29.95K</t>
-        </is>
-      </c>
-      <c r="G77" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H77" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B78" s="5" t="n">
-        <v>29787.18</v>
-      </c>
-      <c r="C78" s="5" t="n">
-        <v>29890</v>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E78" s="8" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="F78" s="6" t="inlineStr">
-        <is>
-          <t>+$29.95K</t>
-        </is>
-      </c>
-      <c r="G78" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H78" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B79" s="5" t="n">
-        <v>29717.18</v>
-      </c>
-      <c r="C79" s="5" t="n">
-        <v>29820</v>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E79" s="7" t="inlineStr">
-        <is>
-          <t>-$10.78K</t>
-        </is>
-      </c>
-      <c r="F79" s="6" t="inlineStr">
-        <is>
-          <t>+$10.78K</t>
-        </is>
-      </c>
-      <c r="G79" s="6" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H79" s="6" t="inlineStr">
+      <c r="H79" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
